--- a/Configs/passive_effect_config.xlsx
+++ b/Configs/passive_effect_config.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="passive_effect_config" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>icon</t>
-  </si>
-  <si>
-    <t>rarity</t>
   </si>
   <si>
     <t>effectType</t>
@@ -273,14 +270,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -736,148 +726,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1229,7 +1219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.875" customWidth="1"/>
@@ -1237,7 +1227,7 @@
     <col min="4" max="4" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1268,338 +1258,308 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>15</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
         <v>500</v>
       </c>
-      <c r="J5" t="b">
+      <c r="I5" t="b">
         <v>0</v>
       </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
         <v>10</v>
       </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
         <v>30</v>
       </c>
-      <c r="J7" t="b">
+      <c r="I7" t="b">
         <v>0</v>
       </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
         <v>15</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>2</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
       <c r="E11">
         <v>1</v>
       </c>
@@ -1610,106 +1570,97 @@
         <v>1</v>
       </c>
       <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11">
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12">
-        <v>2</v>
-      </c>
-      <c r="I12">
         <v>1000</v>
       </c>
-      <c r="J12" t="b">
+      <c r="I12" t="b">
         <v>0</v>
       </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="D13" t="s">
-        <v>47</v>
-      </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
         <v>25</v>
       </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>49</v>
       </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1717,328 +1668,298 @@
       <c r="H14">
         <v>1</v>
       </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14">
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>52</v>
       </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
         <v>15</v>
       </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>55</v>
       </c>
-      <c r="D16" t="s">
-        <v>56</v>
-      </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
         <v>25</v>
       </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>58</v>
       </c>
-      <c r="D17" t="s">
-        <v>59</v>
-      </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
         <v>20</v>
       </c>
-      <c r="J17" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
         <v>60</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>61</v>
       </c>
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
         <v>10</v>
       </c>
-      <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
         <v>63</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>64</v>
       </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>2</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
         <v>66</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" t="s">
-        <v>68</v>
-      </c>
       <c r="E20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>2</v>
-      </c>
-      <c r="I20">
         <v>800</v>
       </c>
-      <c r="J20" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
         <v>69</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>70</v>
       </c>
-      <c r="D21" t="s">
-        <v>71</v>
-      </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
         <v>15</v>
       </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
         <v>72</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>73</v>
       </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
         <v>10</v>
       </c>
-      <c r="J22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
         <v>75</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>76</v>
       </c>
-      <c r="D23" t="s">
-        <v>77</v>
-      </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23">
         <v>50</v>
       </c>
-      <c r="J23" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23">
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23">
         <v>2</v>
       </c>
     </row>

--- a/Configs/passive_effect_config.xlsx
+++ b/Configs/passive_effect_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="76">
   <si>
     <t>id</t>
   </si>
@@ -35,25 +35,25 @@
     <t>name</t>
   </si>
   <si>
-    <t>description</t>
+    <t>des</t>
   </si>
   <si>
     <t>icon</t>
   </si>
   <si>
-    <t>effectType</t>
-  </si>
-  <si>
-    <t>targetAttrId</t>
-  </si>
-  <si>
-    <t>valueType</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>stackable</t>
+    <t>color</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>passives</t>
+  </si>
+  <si>
+    <t>addGold</t>
+  </si>
+  <si>
+    <t>stackType</t>
   </si>
   <si>
     <t>maxStack</t>
@@ -65,10 +65,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>bool</t>
+    <t>int[]</t>
   </si>
   <si>
     <t>虚空之心</t>
@@ -1225,6 +1222,8 @@
     <col min="2" max="2" width="10.875" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="24.875" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1279,13 +1278,13 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
@@ -1296,31 +1295,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>20</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
       <c r="J3">
-        <v>3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1328,31 +1315,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
       </c>
       <c r="E4">
         <v>1</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1360,30 +1332,15 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>500</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5">
         <v>1</v>
       </c>
     </row>
@@ -1392,31 +1349,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
       </c>
       <c r="E6">
         <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1424,30 +1366,15 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
       <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>30</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -1456,31 +1383,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
       </c>
       <c r="E8">
         <v>1</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1488,31 +1400,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
       </c>
       <c r="E9">
         <v>1</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1520,31 +1417,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
       </c>
       <c r="E10">
         <v>1</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1552,31 +1434,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
       </c>
       <c r="E11">
         <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1584,30 +1451,15 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
       <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>1000</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12">
         <v>1</v>
       </c>
     </row>
@@ -1616,31 +1468,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
       </c>
       <c r="E13">
         <v>1</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>25</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1648,31 +1485,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
       </c>
       <c r="E14">
         <v>3</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1680,30 +1502,15 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>51</v>
       </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
       <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>15</v>
-      </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15">
         <v>2</v>
       </c>
     </row>
@@ -1712,255 +1519,135 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
         <v>53</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>54</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>25</v>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
         <v>56</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>57</v>
-      </c>
-      <c r="D17" t="s">
-        <v>58</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>20</v>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
         <v>59</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>10</v>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
         <v>62</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>63</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
-      <c r="F19">
-        <v>4</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
         <v>65</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>66</v>
-      </c>
-      <c r="D20" t="s">
-        <v>67</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
-      <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20">
-        <v>800</v>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
         <v>68</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>69</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>15</v>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
         <v>71</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>72</v>
-      </c>
-      <c r="D22" t="s">
-        <v>73</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>10</v>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
         <v>74</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>75</v>
-      </c>
-      <c r="D23" t="s">
-        <v>76</v>
       </c>
       <c r="E23">
         <v>3</v>
-      </c>
-      <c r="F23">
-        <v>6</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>50</v>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/passive_effect_config.xlsx
+++ b/Configs/passive_effect_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -1307,7 +1307,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>99</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1326,6 +1326,9 @@
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="J4">
+        <v>-1</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
@@ -1343,6 +1346,9 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="J5">
+        <v>-1</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
@@ -1360,6 +1366,9 @@
       <c r="E6">
         <v>1</v>
       </c>
+      <c r="J6">
+        <v>-1</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
@@ -1377,6 +1386,9 @@
       <c r="E7">
         <v>1</v>
       </c>
+      <c r="J7">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
@@ -1394,6 +1406,9 @@
       <c r="E8">
         <v>1</v>
       </c>
+      <c r="J8">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
@@ -1411,6 +1426,9 @@
       <c r="E9">
         <v>1</v>
       </c>
+      <c r="J9">
+        <v>-1</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
@@ -1428,6 +1446,9 @@
       <c r="E10">
         <v>1</v>
       </c>
+      <c r="J10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
@@ -1445,6 +1466,9 @@
       <c r="E11">
         <v>1</v>
       </c>
+      <c r="J11">
+        <v>-1</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
@@ -1462,6 +1486,9 @@
       <c r="E12">
         <v>1</v>
       </c>
+      <c r="J12">
+        <v>-1</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
@@ -1479,6 +1506,9 @@
       <c r="E13">
         <v>1</v>
       </c>
+      <c r="J13">
+        <v>-1</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
@@ -1496,6 +1526,9 @@
       <c r="E14">
         <v>3</v>
       </c>
+      <c r="J14">
+        <v>-1</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
@@ -1513,6 +1546,9 @@
       <c r="E15">
         <v>2</v>
       </c>
+      <c r="J15">
+        <v>-1</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
@@ -1530,8 +1566,11 @@
       <c r="E16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="J16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1547,8 +1586,11 @@
       <c r="E17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="J17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1564,8 +1606,11 @@
       <c r="E18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="J18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1581,8 +1626,11 @@
       <c r="E19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="J19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1598,8 +1646,11 @@
       <c r="E20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="J20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1615,8 +1666,11 @@
       <c r="E21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="J21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1632,8 +1686,11 @@
       <c r="E22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="J22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1648,6 +1705,9 @@
       </c>
       <c r="E23">
         <v>3</v>
+      </c>
+      <c r="J23">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
